--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487152_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487152_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.405200000000001</v>
+        <v>9.7864</v>
       </c>
       <c r="E2" t="n">
-        <v>10.084</v>
+        <v>11.3045</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6788</v>
+        <v>-1.5181</v>
       </c>
       <c r="G2" t="n">
         <v>4.6696</v>
@@ -610,13 +610,13 @@
         <v>3.8602</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6155</v>
+        <v>-0.2343</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5076000000000001</v>
+        <v>0.7129</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.1078</v>
+        <v>-0.9472</v>
       </c>
       <c r="V2" t="n">
         <v>2.4559</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.865</v>
+        <v>4.8949</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9455</v>
+        <v>3.0022</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9195</v>
+        <v>1.8927</v>
       </c>
       <c r="G3" t="n">
         <v>2.9354</v>
@@ -688,13 +688,13 @@
         <v>3.0881</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7715</v>
+        <v>0.8015</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1728</v>
+        <v>1.2295</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4013</v>
+        <v>-0.428</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0649</v>
+        <v>0.0154</v>
       </c>
       <c r="E4" t="n">
         <v>-0.1785</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1136</v>
+        <v>0.1939</v>
       </c>
       <c r="G4" t="n">
         <v>0.06</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1249</v>
+        <v>-0.0446</v>
       </c>
       <c r="T4" t="n">
         <v>-0.1785</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0535</v>
+        <v>0.1338</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CARRETERO GARCIA</t>
+          <t>A. TOURE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2491</v>
+        <v>-0.0183</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4926</v>
+        <v>-2.1421</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7417</v>
+        <v>2.1238</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0207</v>
+        <v>-0.2017</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6312</v>
+        <v>-1.1592</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6105</v>
+        <v>0.9575</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5951</v>
+        <v>0.406</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5058</v>
+        <v>0.2432</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0893</v>
+        <v>0.1628</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6158</v>
+        <v>-0.6076</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.137</v>
+        <v>-1.4023</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5212</v>
+        <v>0.7947</v>
       </c>
       <c r="P5" t="n">
-        <v>0.772</v>
+        <v>-0.386</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9301</v>
+        <v>-2.8951</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7021</v>
+        <v>2.5091</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7145</v>
+        <v>0.5271</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8276</v>
+        <v>0.347</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.5421</v>
+        <v>0.1801</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2859</v>
+        <v>0.0422</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2859</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TOURE</t>
+          <t>D. CARRETERO GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7788</v>
+        <v>-0.3294</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.1435</v>
+        <v>0.0107</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3648</v>
+        <v>-0.3401</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2017</v>
+        <v>-0.0207</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1592</v>
+        <v>-0.6312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9575</v>
+        <v>0.6105</v>
       </c>
       <c r="J6" t="n">
-        <v>0.406</v>
+        <v>1.5951</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2432</v>
+        <v>1.5058</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1628</v>
+        <v>0.0893</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6076</v>
+        <v>-1.6158</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4023</v>
+        <v>-2.137</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7947</v>
+        <v>0.5212</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.386</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8951</v>
+        <v>-1.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5091</v>
+        <v>2.7021</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2333</v>
+        <v>-0.7948</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6544</v>
+        <v>0.3457</v>
       </c>
       <c r="U6" t="n">
-        <v>0.421</v>
+        <v>-1.1406</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0422</v>
+        <v>-0.2859</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0422</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1048</v>
+        <v>-0.8709</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.848</v>
+        <v>-1.7478</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7431</v>
+        <v>0.877</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4788</v>
@@ -1000,13 +1000,13 @@
         <v>0.772</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4752</v>
+        <v>-0.2413</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2974</v>
+        <v>-0.1973</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1778</v>
+        <v>-0.044</v>
       </c>
       <c r="V7" t="n">
         <v>0.0422</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0734</v>
+        <v>-2.1057</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6339</v>
+        <v>-0.7733</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4395</v>
+        <v>-1.3324</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0476</v>
@@ -1078,13 +1078,13 @@
         <v>2.5091</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8051</v>
+        <v>0.1626</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0317</v>
+        <v>0.8289</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7734</v>
+        <v>-0.6663</v>
       </c>
       <c r="V8" t="n">
         <v>-1.7997</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2795</v>
+        <v>-3.6275</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5903</v>
+        <v>-1.8312</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6891</v>
+        <v>-1.7962</v>
       </c>
       <c r="G9" t="n">
         <v>-2.9888</v>
@@ -1156,13 +1156,13 @@
         <v>2.1231</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7443</v>
+        <v>0.3963</v>
       </c>
       <c r="T9" t="n">
-        <v>1.125</v>
+        <v>0.8841</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3808</v>
+        <v>-0.4878</v>
       </c>
       <c r="V9" t="n">
         <v>-1.228</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0777</v>
+        <v>-4.8248</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1258</v>
+        <v>-2.7659</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9519</v>
+        <v>-2.059</v>
       </c>
       <c r="G10" t="n">
         <v>-0.3559</v>
@@ -1234,13 +1234,13 @@
         <v>1.7371</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0655</v>
+        <v>-0.8127</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9518</v>
+        <v>-0.5919</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1137</v>
+        <v>-0.2208</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4982</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4725</v>
+        <v>-6.1556</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.5346</v>
+        <v>-1.8162</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9379</v>
+        <v>-4.3395</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8424</v>
@@ -1312,13 +1312,13 @@
         <v>1.9301</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4012</v>
+        <v>-0.2819</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5169</v>
+        <v>0.2353</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1157</v>
+        <v>-0.5173</v>
       </c>
       <c r="V11" t="n">
         <v>-4.9964</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.830499999999999</v>
+        <v>-3.2355</v>
       </c>
       <c r="E12" t="n">
-        <v>2.467499999999998</v>
+        <v>3.0624</v>
       </c>
       <c r="F12" t="n">
         <v>-6.2979</v>
@@ -1360,7 +1360,7 @@
         <v>-4.072800000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>4.801699999999999</v>
+        <v>4.8017</v>
       </c>
       <c r="J12" t="n">
         <v>12.3796</v>
@@ -1381,7 +1381,7 @@
         <v>3.2418</v>
       </c>
       <c r="P12" t="n">
-        <v>4.825100000000001</v>
+        <v>4.8251</v>
       </c>
       <c r="Q12" t="n">
         <v>-16.4056</v>
@@ -1390,10 +1390,10 @@
         <v>21.2309</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.117</v>
+        <v>-0.5221</v>
       </c>
       <c r="T12" t="n">
-        <v>3.0209</v>
+        <v>3.6157</v>
       </c>
       <c r="U12" t="n">
         <v>-4.138100000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8846</v>
+        <v>5.1137</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8581</v>
+        <v>4.6592</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0265</v>
+        <v>0.4545</v>
       </c>
       <c r="G13" t="n">
         <v>2.382</v>
@@ -1468,13 +1468,13 @@
         <v>2.5091</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.5553</v>
+        <v>-0.3262</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4323</v>
+        <v>0.3689</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.123</v>
+        <v>-0.6951000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.5138</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.144</v>
+        <v>3.2664</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7913</v>
+        <v>3.3081</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3527</v>
+        <v>-0.0417</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6272</v>
+        <v>3.6516</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.8061</v>
+        <v>2.8876</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1788</v>
+        <v>0.764</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2132</v>
+        <v>6.1141</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.8643999999999999</v>
+        <v>4.7711</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6512</v>
+        <v>1.3431</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.4141</v>
+        <v>-2.4625</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9417</v>
+        <v>-1.8834</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>0.386</v>
+        <v>-2.1231</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.965</v>
+        <v>-5.0182</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3511</v>
+        <v>2.8951</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0994</v>
+        <v>0.5099</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6837</v>
+        <v>0.6984</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4157</v>
+        <v>-0.1884</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2859</v>
+        <v>1.228</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>1.5138</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.0209</v>
+        <v>1.2807</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6071</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4137</v>
+        <v>1.1918</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6516</v>
+        <v>-0.6272</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8876</v>
+        <v>-1.8061</v>
       </c>
       <c r="I15" t="n">
-        <v>0.764</v>
+        <v>1.1788</v>
       </c>
       <c r="J15" t="n">
-        <v>6.1141</v>
+        <v>-0.2132</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7711</v>
+        <v>-0.8643999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3431</v>
+        <v>0.6512</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.4625</v>
+        <v>-0.4141</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8834</v>
+        <v>-0.9417</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.1231</v>
+        <v>0.386</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.0182</v>
+        <v>-0.965</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8951</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2644</v>
+        <v>1.236</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0026</v>
+        <v>0.9813</v>
       </c>
       <c r="U15" t="n">
-        <v>0.267</v>
+        <v>0.2548</v>
       </c>
       <c r="V15" t="n">
-        <v>1.228</v>
+        <v>0.2859</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5138</v>
+        <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2957</v>
+        <v>-0.4533</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5076</v>
+        <v>1.705</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2119</v>
+        <v>-2.1584</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8998</v>
@@ -1702,13 +1702,13 @@
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2606</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>2.6982</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4376</v>
+        <v>-0.3841</v>
       </c>
       <c r="V16" t="n">
         <v>0.8999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. SOUZA FIGUEIREDO</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0048</v>
+        <v>-0.6714</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9379999999999999</v>
+        <v>-1.5919</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0668</v>
+        <v>0.9205</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.2295</v>
+        <v>-2.7194</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7297</v>
+        <v>1.6311</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4998</v>
+        <v>-4.3505</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3683</v>
+        <v>-1.8388</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2586</v>
+        <v>2.0854</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6269</v>
+        <v>-3.9242</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8612</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9883</v>
+        <v>-0.4542</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1271</v>
+        <v>-0.4263</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3161</v>
+        <v>1.158</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.8951</v>
+        <v>-0.193</v>
       </c>
       <c r="R17" t="n">
-        <v>0.579</v>
+        <v>1.3511</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.201</v>
+        <v>-0.0522</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4164</v>
+        <v>0.154</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2155</v>
+        <v>-0.2062</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7418</v>
+        <v>0.9421</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7418</v>
+        <v>0.2859</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.6562</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.212</v>
+        <v>-0.7711</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7502</v>
+        <v>-1.5499</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5382</v>
+        <v>0.7788</v>
       </c>
       <c r="G18" t="n">
         <v>1.7608</v>
@@ -1858,13 +1858,13 @@
         <v>2.5091</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4178</v>
+        <v>0.0231</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2353</v>
+        <v>0.4356</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6531</v>
+        <v>-0.4125</v>
       </c>
       <c r="V18" t="n">
         <v>1.8842</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>P. SOUZA FIGUEIREDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2939</v>
+        <v>-0.8184</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6728</v>
+        <v>-0.5374</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9667</v>
+        <v>-0.2809</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7105</v>
+        <v>-1.2295</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2781</v>
+        <v>-0.7297</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4323</v>
+        <v>-0.4998</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5553</v>
+        <v>-0.3683</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0309</v>
+        <v>0.2586</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-0.6269</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1552</v>
+        <v>-0.8612</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3091</v>
+        <v>-0.9883</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8461</v>
+        <v>0.1271</v>
       </c>
       <c r="P19" t="n">
-        <v>1.9301</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.193</v>
+        <v>-2.8951</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1231</v>
+        <v>0.579</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4713</v>
+        <v>-0.0145</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2353</v>
+        <v>-0.0159</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7066</v>
+        <v>0.0013</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0422</v>
+        <v>2.7418</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1857</v>
+        <v>2.7418</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5935</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1928</v>
+        <v>0.9732</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5993000000000001</v>
+        <v>-1.8064</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7194</v>
+        <v>-2.7105</v>
       </c>
       <c r="H20" t="n">
-        <v>1.6311</v>
+        <v>-1.2781</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.3505</v>
+        <v>-1.4323</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8388</v>
+        <v>-0.5553</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0854</v>
+        <v>0.0309</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.9242</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8804999999999999</v>
+        <v>-2.1552</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4542</v>
+        <v>-1.3091</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4263</v>
+        <v>-0.8461</v>
       </c>
       <c r="P20" t="n">
-        <v>1.158</v>
+        <v>1.9301</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.193</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3511</v>
+        <v>2.1231</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.0106</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4468</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5275</v>
+        <v>-0.5463</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9421</v>
+        <v>-0.0422</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2859</v>
+        <v>1.1857</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6562</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4106</v>
+        <v>-1.5153</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.258</v>
+        <v>-0.6571</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1527</v>
+        <v>-0.8582</v>
       </c>
       <c r="G21" t="n">
         <v>-0.3372</v>
@@ -2092,13 +2092,13 @@
         <v>0.965</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8877</v>
+        <v>0.0076</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4164</v>
+        <v>0.1844</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4713</v>
+        <v>-0.1768</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1857</v>
@@ -2125,22 +2125,22 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3.8304</v>
+        <v>4.5981</v>
       </c>
       <c r="E22" t="n">
-        <v>6.297899999999999</v>
+        <v>6.398100000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4677</v>
+        <v>-1.8</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7291999999999994</v>
+        <v>-0.7292000000000003</v>
       </c>
       <c r="H22" t="n">
         <v>4.0726</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.8018</v>
+        <v>-4.801799999999999</v>
       </c>
       <c r="J22" t="n">
         <v>11.6504</v>
@@ -2149,7 +2149,7 @@
         <v>14.8921</v>
       </c>
       <c r="L22" t="n">
-        <v>-3.241499999999999</v>
+        <v>-3.2415</v>
       </c>
       <c r="M22" t="n">
         <v>-12.3796</v>
@@ -2161,7 +2161,7 @@
         <v>-1.5602</v>
       </c>
       <c r="P22" t="n">
-        <v>-4.825200000000001</v>
+        <v>-4.8252</v>
       </c>
       <c r="Q22" t="n">
         <v>-21.2307</v>
@@ -2170,13 +2170,13 @@
         <v>16.4057</v>
       </c>
       <c r="S22" t="n">
-        <v>1.117</v>
+        <v>1.8847</v>
       </c>
       <c r="T22" t="n">
-        <v>4.137999999999999</v>
+        <v>4.238200000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-3.0209</v>
+        <v>-2.3533</v>
       </c>
       <c r="V22" t="n">
         <v>8.267799999999999</v>
